--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -403,10 +403,10 @@
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-    <col min="8" max="8" width="50.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -432,7 +432,7 @@
         <v>Video 3</v>
       </c>
       <c r="H1" t="str">
-        <v>Summary</v>
+        <v>comments</v>
       </c>
     </row>
     <row r="2">
@@ -510,7 +510,7 @@
         <v>—</v>
       </c>
       <c r="H4" t="str">
-        <v>Video 1 has no passing metrics</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -536,7 +536,7 @@
         <v>—</v>
       </c>
       <c r="H5" t="str">
-        <v>Video 2 has no passing metrics</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -692,7 +692,7 @@
         <v>Yes</v>
       </c>
       <c r="H11" t="str">
-        <v>Video 1 has Brightness, Noise: Slight, Avg, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
         <v>Yes</v>
       </c>
       <c r="H12" t="str">
-        <v>Video 2 has Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -744,7 +744,7 @@
         <v>Yes</v>
       </c>
       <c r="H13" t="str">
-        <v>Video 3 has Wobble, Jitter, Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -874,7 +874,7 @@
         <v>Yes</v>
       </c>
       <c r="H18" t="str">
-        <v>Video 1 has Jitter, Noise</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -900,7 +900,7 @@
         <v>Yes</v>
       </c>
       <c r="H19" t="str">
-        <v>Video 2 has Wobble, Jitter, Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -926,7 +926,7 @@
         <v>Yes</v>
       </c>
       <c r="H20" t="str">
-        <v>Video 3 has Wobble, Jitter, Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1056,7 +1056,7 @@
         <v>Yes</v>
       </c>
       <c r="H25" t="str">
-        <v>Video 1 has Brightness, Noise: Slight, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1082,7 +1082,7 @@
         <v>Yes</v>
       </c>
       <c r="H26" t="str">
-        <v>Video 2 has Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1108,7 +1108,7 @@
         <v>Yes</v>
       </c>
       <c r="H27" t="str">
-        <v>Video 3 has Wobble, Jitter, Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1238,7 +1238,7 @@
         <v>—</v>
       </c>
       <c r="H32" t="str">
-        <v>Video 1 has Brightness, Noise: Slight, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1264,7 +1264,7 @@
         <v>—</v>
       </c>
       <c r="H33" t="str">
-        <v>Video 2 has Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1420,7 +1420,7 @@
         <v>Yes</v>
       </c>
       <c r="H39" t="str">
-        <v>Video 1 has Brightness, Noise: Slight, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1446,7 +1446,7 @@
         <v>Yes</v>
       </c>
       <c r="H40" t="str">
-        <v>Video 2 has Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -1472,7 +1472,7 @@
         <v>Yes</v>
       </c>
       <c r="H41" t="str">
-        <v>Video 3 has Wobble, Jitter, Brightness, Noise, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -1602,7 +1602,7 @@
         <v>Yes</v>
       </c>
       <c r="H46" t="str">
-        <v>Video 1 has Jitter: Not good, Brightness, Noise: Slight, Stability</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -1619,16 +1619,16 @@
         <v>Jitter</v>
       </c>
       <c r="E47" t="str">
-        <v>No (Not good)</v>
+        <v>No</v>
       </c>
       <c r="F47" t="str">
         <v>No</v>
       </c>
       <c r="G47" t="str">
-        <v>Yes (Excellent)</v>
+        <v>Yes</v>
       </c>
       <c r="H47" t="str">
-        <v>Video 2 has Brightness (very good), Noise, Stability</v>
+        <v>Video 3: Very good</v>
       </c>
     </row>
     <row r="48">
@@ -1645,16 +1645,16 @@
         <v>Brightness</v>
       </c>
       <c r="E48" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="F48" t="str">
-        <v>Yes (very good)</v>
+        <v>Yes</v>
       </c>
       <c r="G48" t="str">
         <v>Yes</v>
       </c>
       <c r="H48" t="str">
-        <v>Video 3 has Wobble, Jitter (Excellent), Brightness, Noise, Stability</v>
+        <v>Video 1: not real, Video 2: Real</v>
       </c>
     </row>
     <row r="49">

--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -1605,7 +1605,7 @@
         <v/>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
         <v/>
       </c>
@@ -1627,8 +1627,10 @@
       <c r="G47" t="str">
         <v>Yes</v>
       </c>
-      <c r="H47" t="str">
-        <v>Video 3: Very good</v>
+      <c r="H47" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. this is not real
+2. colour problem
+3. this feels real</v>
       </c>
     </row>
     <row r="48">
@@ -1645,7 +1647,7 @@
         <v>Brightness</v>
       </c>
       <c r="E48" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F48" t="str">
         <v>Yes</v>
@@ -1654,7 +1656,7 @@
         <v>Yes</v>
       </c>
       <c r="H48" t="str">
-        <v>Video 1: not real, Video 2: Real</v>
+        <v/>
       </c>
     </row>
     <row r="49">

--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -1605,7 +1605,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" xml:space="preserve">
+    <row r="47">
       <c r="A47" t="str">
         <v/>
       </c>
@@ -1627,10 +1627,8 @@
       <c r="G47" t="str">
         <v>Yes</v>
       </c>
-      <c r="H47" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. this is not real
-2. colour problem
-3. this feels real</v>
+      <c r="H47" t="str">
+        <v>1. Excellent</v>
       </c>
     </row>
     <row r="48">
@@ -1656,7 +1654,7 @@
         <v>Yes</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>1. Good</v>
       </c>
     </row>
     <row r="49">
@@ -1673,7 +1671,7 @@
         <v>Noise</v>
       </c>
       <c r="E49" t="str">
-        <v>Slight</v>
+        <v>It is not real, Slight</v>
       </c>
       <c r="F49" t="str">
         <v>Yes</v>

--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -747,7 +747,7 @@
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" xml:space="preserve">
       <c r="A14" t="str">
         <v/>
       </c>
@@ -760,8 +760,9 @@
       <c r="D14" t="str">
         <v>Noise</v>
       </c>
-      <c r="E14" t="str">
-        <v>Slight, Avg</v>
+      <c r="E14" t="str" xml:space="preserve">
+        <v xml:space="preserve">Slight
+Avg</v>
       </c>
       <c r="F14" t="str">
         <v>Yes</v>
@@ -1581,7 +1582,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Brightlight</v>
+        <v>Brighlight</v>
       </c>
       <c r="B46" t="str">
         <v>1080p</v>
@@ -1654,7 +1655,7 @@
         <v>Yes</v>
       </c>
       <c r="H48" t="str">
-        <v>1. Good</v>
+        <v>1. good</v>
       </c>
     </row>
     <row r="49">
@@ -1671,7 +1672,7 @@
         <v>Noise</v>
       </c>
       <c r="E49" t="str">
-        <v>It is not real, Slight</v>
+        <v>Slight</v>
       </c>
       <c r="F49" t="str">
         <v>Yes</v>

--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -1582,7 +1582,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Brighlight</v>
+        <v>Brightlight</v>
       </c>
       <c r="B46" t="str">
         <v>1080p</v>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
         <v/>
       </c>
@@ -1628,8 +1628,10 @@
       <c r="G47" t="str">
         <v>Yes</v>
       </c>
-      <c r="H47" t="str">
-        <v>1. Excellent</v>
+      <c r="H47" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Not real
+2. Excellent
+3. Very good</v>
       </c>
     </row>
     <row r="48">
@@ -1655,7 +1657,7 @@
         <v>Yes</v>
       </c>
       <c r="H48" t="str">
-        <v>1. good</v>
+        <v/>
       </c>
     </row>
     <row r="49">

--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" xml:space="preserve">
+    <row r="47">
       <c r="A47" t="str">
         <v/>
       </c>
@@ -1628,10 +1628,8 @@
       <c r="G47" t="str">
         <v>Yes</v>
       </c>
-      <c r="H47" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Not real
-2. Excellent
-3. Very good</v>
+      <c r="H47" t="str">
+        <v>1. Good</v>
       </c>
     </row>
     <row r="48">
@@ -1645,19 +1643,19 @@
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>Brightness</v>
+        <v/>
       </c>
       <c r="E48" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F48" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="G48" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>2. Very good</v>
       </c>
     </row>
     <row r="49">
@@ -1671,10 +1669,10 @@
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>Noise</v>
+        <v>Brightness</v>
       </c>
       <c r="E49" t="str">
-        <v>Slight</v>
+        <v>Yes</v>
       </c>
       <c r="F49" t="str">
         <v>Yes</v>
@@ -1697,10 +1695,10 @@
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>Stability</v>
+        <v>Noise</v>
       </c>
       <c r="E50" t="str">
-        <v>Yes</v>
+        <v>Slight</v>
       </c>
       <c r="F50" t="str">
         <v>Yes</v>
@@ -1723,24 +1721,50 @@
         <v/>
       </c>
       <c r="D51" t="str">
-        <v/>
+        <v>Stability</v>
       </c>
       <c r="E51" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="H51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v/>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+      <c r="C52" t="str">
+        <v/>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H52"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1643,19 +1643,19 @@
         <v/>
       </c>
       <c r="D48" t="str">
-        <v/>
+        <v>Brightness</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="H48" t="str">
-        <v>2. Very good</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -1669,10 +1669,10 @@
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>Brightness</v>
+        <v>Noise</v>
       </c>
       <c r="E49" t="str">
-        <v>Yes</v>
+        <v>Slight</v>
       </c>
       <c r="F49" t="str">
         <v>Yes</v>
@@ -1695,10 +1695,10 @@
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>Noise</v>
+        <v>Stability</v>
       </c>
       <c r="E50" t="str">
-        <v>Slight</v>
+        <v>Yes</v>
       </c>
       <c r="F50" t="str">
         <v>Yes</v>
@@ -1721,50 +1721,24 @@
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>Stability</v>
+        <v/>
       </c>
       <c r="E51" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="F51" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="G51" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="H51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v/>
-      </c>
-      <c r="B52" t="str">
-        <v/>
-      </c>
-      <c r="C52" t="str">
-        <v/>
-      </c>
-      <c r="D52" t="str">
-        <v/>
-      </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
-      <c r="G52" t="str">
-        <v/>
-      </c>
-      <c r="H52" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
         <v/>
       </c>
@@ -1628,8 +1628,9 @@
       <c r="G47" t="str">
         <v>Yes</v>
       </c>
-      <c r="H47" t="str">
-        <v>1. Good</v>
+      <c r="H47" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Good
+2. Very good</v>
       </c>
     </row>
     <row r="48">

--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -1603,10 +1603,10 @@
         <v>Yes</v>
       </c>
       <c r="H46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47" xml:space="preserve">
+        <v>1. Very good</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="str">
         <v/>
       </c>
@@ -1628,9 +1628,8 @@
       <c r="G47" t="str">
         <v>Yes</v>
       </c>
-      <c r="H47" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Good
-2. Very good</v>
+      <c r="H47" t="str">
+        <v>2. Excellent</v>
       </c>
     </row>
     <row r="48">

--- a/reports/PRISM_Report_2026-06-11.xlsx
+++ b/reports/PRISM_Report_2026-06-11.xlsx
@@ -1629,7 +1629,7 @@
         <v>Yes</v>
       </c>
       <c r="H47" t="str">
-        <v>2. Excellent</v>
+        <v>2. bad</v>
       </c>
     </row>
     <row r="48">
@@ -1655,7 +1655,7 @@
         <v>Yes</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>3. Excellent</v>
       </c>
     </row>
     <row r="49">
@@ -1681,7 +1681,7 @@
         <v>Yes</v>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>4. gooooood</v>
       </c>
     </row>
     <row r="50">
